--- a/output/xlsx/data_combined.xlsx
+++ b/output/xlsx/data_combined.xlsx
@@ -1217,7 +1217,7 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>0.7476</v>
+        <v>74.76000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1265,7 +1265,7 @@
         <v>12</v>
       </c>
       <c r="L19">
-        <v>0.607</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="20">
@@ -1313,7 +1313,7 @@
         <v>6</v>
       </c>
       <c r="L20">
-        <v>0.6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
@@ -1361,7 +1361,7 @@
         <v>2</v>
       </c>
       <c r="L21">
-        <v>0.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -1409,7 +1409,7 @@
         <v>6</v>
       </c>
       <c r="L22">
-        <v>0.5133</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="23">
@@ -1457,7 +1457,7 @@
         <v>2</v>
       </c>
       <c r="L23">
-        <v>0.5375</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="24">
@@ -1505,7 +1505,7 @@
         <v>2</v>
       </c>
       <c r="L24">
-        <v>0.2082</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="25">
@@ -1553,7 +1553,7 @@
         <v>2</v>
       </c>
       <c r="L25">
-        <v>0.226</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="26">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="L26">
-        <v>0.4175</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="27">
@@ -1649,7 +1649,7 @@
         <v>5</v>
       </c>
       <c r="L27">
-        <v>0.4417</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="28">
@@ -1697,7 +1697,7 @@
         <v>2</v>
       </c>
       <c r="L28">
-        <v>0.378</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="29">
@@ -1745,7 +1745,7 @@
         <v>3</v>
       </c>
       <c r="L29">
-        <v>0.4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
@@ -1793,7 +1793,7 @@
         <v>3</v>
       </c>
       <c r="L30">
-        <v>0.475</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="31">
@@ -1841,7 +1841,7 @@
         <v>3</v>
       </c>
       <c r="L31">
-        <v>0.5660000000000001</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="32">
@@ -1889,7 +1889,7 @@
         <v>4</v>
       </c>
       <c r="L32">
-        <v>0.225</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="33">
@@ -1937,7 +1937,7 @@
         <v>3</v>
       </c>
       <c r="L33">
-        <v>0.3225</v>
+        <v>32.25</v>
       </c>
     </row>
   </sheetData>
